--- a/artfynd/A 43362-2022 artfynd.xlsx
+++ b/artfynd/A 43362-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43362-2022 artfynd.xlsx
+++ b/artfynd/A 43362-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106851387</v>
+        <v>107829820</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svackan, Löftabrovägen, Löftabro, Stråvalla, Hl</t>
+          <t>Löftabrovägen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329948.558100713</v>
+        <v>329907</v>
       </c>
       <c r="R2" t="n">
-        <v>6355245.062483793</v>
+        <v>6355233</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,60 +752,549 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Arten är den lilla brunsvarta fladdermusen. Arten har funnits i området flera årtionden, långt före 1980-talet. De jagar insekter i detta lätt fuktiga skogsparti på sommarkvällarna.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lätt fuktig lövskog, asp som dominant. Numera mycket sly från asp.Norr om vägen liknande område med enstaka gamla bokar. Brant bergsbacke som håller området fuktigt.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johanna Michaëlsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Johanna Michaëlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113093220</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Löftabrovägen, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>329907</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6355233</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Michaëlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Michaëlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106851387</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svackan, Löftabrovägen, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>329949</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6355246</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Arten är den lilla brunsvarta fladdermusen. Arten har funnits i området flera årtionden, långt före 1980-talet. De jagar insekter i detta lätt fuktiga skogsparti på sommarkvällarna.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lövträd</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lätt fuktig lövskog, asp som dominant. Numera mycket sly från asp.Norr om vägen liknande område med enstaka gamla bokar. Brant bergsbacke som håller området fuktigt.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Antti Friberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Antti Friberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107045436</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södra Kapelliden, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>330152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6355234</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fladdermusen flyger utmed Kapelliden för att leta efter ytterligare föda vid nedanför liggande Löftabrovägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118944637</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Järnvägsundergång, Löftabrovägen-Skareviksvägen, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>329582</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6355047</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>-flera fladdermöss som flyger i midsommarnatten</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
